--- a/modules/EEEE4077_mechatronics_proj/chapters/deliverables/assets/gantt_chart.xlsx
+++ b/modules/EEEE4077_mechatronics_proj/chapters/deliverables/assets/gantt_chart.xlsx
@@ -249,6 +249,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -676,11 +679,15 @@
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="J1:P1"/>
   </mergeCells>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -933,5 +940,6 @@
       </c>
     </row>
   </sheetData>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>